--- a/data/trans_orig/P77_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P77_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según cual es la persona sustentadora principal del hogar en 2023</t>
+          <t>Población según cual es la persona sustentadora principal del hogar en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44155</t>
+          <t>43249</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92310</t>
+          <t>92850</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>109398</t>
+          <t>108584</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>138870</t>
+          <t>137994</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>160892</t>
+          <t>162075</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>216135</t>
+          <t>219235</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,47%</t>
         </is>
       </c>
     </row>
@@ -843,97 +843,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1032</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1327</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>219133</t>
+          <t>218593</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>267288</t>
+          <t>268194</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>150765</t>
+          <t>151641</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>180237</t>
+          <t>181051</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>384942</t>
+          <t>381842</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>440185</t>
+          <t>439002</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,04%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>76715</t>
+          <t>79317</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>138143</t>
+          <t>144801</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>217552</t>
+          <t>217765</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>258848</t>
+          <t>258681</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>306728</t>
+          <t>309407</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>386338</t>
+          <t>381486</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>36,92%</t>
         </is>
       </c>
     </row>
@@ -1299,97 +1299,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2598</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1377</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1804</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>380247</t>
+          <t>373589</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>441675</t>
+          <t>439073</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>256121</t>
+          <t>256288</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>297417</t>
+          <t>297204</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>647021</t>
+          <t>651873</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>726631</t>
+          <t>723952</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,06%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42714</t>
+          <t>42261</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74443</t>
+          <t>72931</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>138913</t>
+          <t>140009</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>170866</t>
+          <t>172055</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>188261</t>
+          <t>188977</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>236006</t>
+          <t>236556</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,56%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12242</t>
+          <t>11013</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1196</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9490</t>
+          <t>11300</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2587</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15676</t>
+          <t>16571</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>239601</t>
+          <t>239358</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>273139</t>
+          <t>272040</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>174341</t>
+          <t>173494</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>206881</t>
+          <t>204883</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>424443</t>
+          <t>420191</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>471866</t>
+          <t>468873</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>70,49%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29828</t>
+          <t>27812</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73463</t>
+          <t>72955</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>97183</t>
+          <t>106780</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>217815</t>
+          <t>218328</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>159458</t>
+          <t>155392</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>256881</t>
+          <t>255817</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,45%</t>
         </is>
       </c>
     </row>
@@ -2211,97 +2211,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2047</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1522</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1697</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>239094</t>
+          <t>239602</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>282729</t>
+          <t>284745</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>257903</t>
+          <t>257390</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>378535</t>
+          <t>368938</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>531393</t>
+          <t>532457</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>628816</t>
+          <t>632882</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>80,29%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11327</t>
+          <t>11112</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30502</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31152</t>
+          <t>33547</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>77713</t>
+          <t>79158</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50686</t>
+          <t>53173</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>95423</t>
+          <t>96131</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>142459</t>
+          <t>142481</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3361</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>173742</t>
+          <t>154146</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>35,23%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>147908</t>
+          <t>148311</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>166763</t>
+          <t>166884</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>82347</t>
+          <t>81002</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>184534</t>
+          <t>184737</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>209249</t>
+          <t>222566</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>347737</t>
+          <t>348225</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,59%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35369</t>
+          <t>36146</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>63050</t>
+          <t>62944</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>110949</t>
+          <t>112105</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>136118</t>
+          <t>137718</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>152525</t>
+          <t>152977</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>190420</t>
+          <t>192080</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,47%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>842</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9775</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>15156</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6051</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20996</t>
+          <t>19610</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>203212</t>
+          <t>202426</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>231065</t>
+          <t>230289</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>112510</t>
+          <t>112744</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>137818</t>
+          <t>137875</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>324408</t>
+          <t>321620</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>362602</t>
+          <t>363588</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>69,03%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>83664</t>
+          <t>85029</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>143448</t>
+          <t>141756</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>301101</t>
+          <t>302678</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>622913</t>
+          <t>650087</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>390964</t>
+          <t>391731</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>906213</t>
+          <t>871804</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>59,16%</t>
         </is>
       </c>
     </row>
@@ -3579,97 +3579,97 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>1312</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>4374</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>1312</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="S29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>5203</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>4588</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>1312</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>4656</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>480831</t>
+          <t>482523</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>540615</t>
+          <t>539250</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>225714</t>
+          <t>198283</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>546396</t>
+          <t>544931</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>564718</t>
+          <t>603754</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1080768</t>
+          <t>1081078</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,37%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>36990</t>
+          <t>35265</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>125924</t>
+          <t>129657</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>352243</t>
+          <t>353548</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>399704</t>
+          <t>399185</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>275325</t>
+          <t>287662</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>557475</t>
+          <t>555437</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,74%</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>13707</t>
+          <t>16273</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,62 +4070,62 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>2649</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>1297</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>14830</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>11916</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>799653</t>
+          <t>795688</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>890165</t>
+          <t>892104</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>318027</t>
+          <t>318546</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>365488</t>
+          <t>364183</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1086549</t>
+          <t>1088088</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1371235</t>
+          <t>1357549</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>82,45%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>432517</t>
+          <t>415608</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>614949</t>
+          <t>615693</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1539669</t>
+          <t>1536398</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2086105</t>
+          <t>2073449</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1994149</t>
+          <t>1996506</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2727441</t>
+          <t>2648552</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>36,93%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>23336</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>13801</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>261254</t>
+          <t>269368</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>21897</t>
+          <t>22895</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>277996</t>
+          <t>272694</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2833918</t>
+          <t>2835359</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3021578</t>
+          <t>3035655</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1558856</t>
+          <t>1582595</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2104820</t>
+          <t>2110337</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>4397831</t>
+          <t>4481377</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5094285</t>
+          <t>5103954</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>71,16%</t>
         </is>
       </c>
     </row>
